--- a/TP/Compras.xlsx
+++ b/TP/Compras.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Curso TSDS\4C\Ingenieria\TP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C6B8B61-23CA-4E33-B890-4FA10047BA00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F56BC827-099A-4DD7-9ACA-C5D09D18BAE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9120" yWindow="1520" windowWidth="24810" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2260" yWindow="1120" windowWidth="30540" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$D$6</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -489,13 +492,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.1796875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="22.90625" style="1" customWidth="1"/>
     <col min="2" max="2" width="41.08984375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="45.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.54296875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="40.08984375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -583,7 +589,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup scale="81" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>